--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>118325901</v>
       </c>
       <c r="B7" t="n">
-        <v>106371</v>
+        <v>106378</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,6 +1399,113 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120159991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallsjön, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>620556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6654256</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,6 +1506,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120332446</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Järpenstorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>620502</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6654270</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Vilhelm Kroon, Thorleif Joelson, Nadja Nilsson, Alexandra Astafourova, Eric Grund, Lennart Henstam, Elin Sjögren Englund, Vilhelm Kroon, Thorleif Joelson, Nadja Nilsson, Alexandra Astafourova, Eric Grund, Lennart Henstam, Elin Sjögren Englund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31628-2023 artfynd.xlsx
+++ b/artfynd/A 31628-2023 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>120159991</v>
       </c>
       <c r="B8" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
